--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file MICROBIOLOGY (#63.05) to Specimen</t>
+    <t>This StructureDefinition contains the maps for VistA file MICROBIOLOGY (63.05) to Specimen</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -496,7 +496,7 @@
     <t>The identifier assigned by the lab when accessioning specimen(s). This is not necessarily the same as the specimen identifier, depending on local lab procedures.</t>
   </si>
   <si>
-    <t>1469: source value from MICROBIOLOGY - MICROBIOLOGY ACCESSION (#63.05-.06)</t>
+    <t>1469: source value from MICROBIOLOGY - MICROBIOLOGY ACCESSION (63.05-.06)</t>
   </si>
   <si>
     <t>Micro.Microbiology.MicrobiologyAccession</t>
@@ -656,7 +656,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1470: source value from MICROBIOLOGY - COLLECTION SAMPLE &gt; COLLECTION SAMPLE - NAME (#63.05-.055 &gt; 62-.01)</t>
+    <t>1470: source value from MICROBIOLOGY - COLLECTION SAMPLE &gt; COLLECTION SAMPLE - NAME (63.05-.055 &gt; 62-.01)</t>
   </si>
   <si>
     <t>Dim.CollectionSample.CollectionSample,Dim.Topography.CollectionSample</t>
@@ -1536,7 +1536,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="111.4375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="109.8984375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="70.17578125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="99.94921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -659,7 +659,8 @@
     <t>1470: source value from MICROBIOLOGY - COLLECTION SAMPLE &gt; COLLECTION SAMPLE - NAME (63.05-.055 &gt; 62-.01)</t>
   </si>
   <si>
-    <t>Dim.CollectionSample.CollectionSample,Dim.Topography.CollectionSample</t>
+    <t>Micro.Microbiology.CollectionSampleIEN
+Dim.CollectionSample.CollectionSample,Dim.Topography.CollectionSample</t>
   </si>
   <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologySpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
